--- a/results/all_images/quantification/quantification_all_images.xlsx
+++ b/results/all_images/quantification/quantification_all_images.xlsx
@@ -620,16 +620,16 @@
         <v>3013</v>
       </c>
       <c r="G2" t="n">
-        <v>8.615399999999999</v>
+        <v>10.9231</v>
       </c>
       <c r="H2" t="n">
-        <v>361.4615</v>
+        <v>422.0769</v>
       </c>
       <c r="I2" t="n">
-        <v>907.3846</v>
+        <v>1022.4615</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03465004</v>
+        <v>0.037413</v>
       </c>
       <c r="K2" t="n">
         <v>297.8123</v>
@@ -647,40 +647,40 @@
         <v>0.9908</v>
       </c>
       <c r="P2" t="n">
-        <v>0.03275532</v>
+        <v>0.03830376</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.0350223</v>
+        <v>0.03934038</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9437</v>
+        <v>3.7216</v>
       </c>
       <c r="S2" t="n">
-        <v>273.3077</v>
+        <v>356.4615</v>
       </c>
       <c r="T2" t="n">
-        <v>501</v>
+        <v>745.8462</v>
       </c>
       <c r="U2" t="n">
-        <v>408.2629</v>
+        <v>478.7993</v>
       </c>
       <c r="V2" t="n">
-        <v>1023.9562</v>
+        <v>1157.4735</v>
       </c>
       <c r="W2" t="n">
-        <v>9.7692</v>
+        <v>9.461499999999999</v>
       </c>
       <c r="X2" t="n">
-        <v>12.5385</v>
+        <v>13.4615</v>
       </c>
       <c r="Y2" t="n">
-        <v>14</v>
+        <v>14.0769</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.03903357</v>
+        <v>0.04234794</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.03451624</v>
+        <v>0.03737811</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -688,22 +688,22 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>6.1924</v>
+        <v>7.3668</v>
       </c>
       <c r="AE2" t="n">
-        <v>6.3246</v>
+        <v>8</v>
       </c>
       <c r="AF2" t="n">
         <v>4</v>
       </c>
       <c r="AG2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AH2" t="n">
-        <v>33745</v>
+        <v>36570</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.7445</v>
+        <v>6.6809</v>
       </c>
     </row>
     <row r="3">
@@ -735,13 +735,13 @@
         <v>8.2727</v>
       </c>
       <c r="H3" t="n">
-        <v>357.0909</v>
+        <v>371.6364</v>
       </c>
       <c r="I3" t="n">
-        <v>968.7273</v>
+        <v>978.9091</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03407276</v>
+        <v>0.03400824</v>
       </c>
       <c r="K3" t="n">
         <v>349.6878</v>
@@ -759,40 +759,40 @@
         <v>0.9555</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02900112</v>
+        <v>0.03007332</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03326266</v>
+        <v>0.03369617</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3636</v>
+        <v>2.4334</v>
       </c>
       <c r="S3" t="n">
-        <v>239.9091</v>
+        <v>286.7273</v>
       </c>
       <c r="T3" t="n">
-        <v>479.8182</v>
+        <v>664.3636</v>
       </c>
       <c r="U3" t="n">
-        <v>397.1731</v>
+        <v>414.3253</v>
       </c>
       <c r="V3" t="n">
-        <v>1090.3199</v>
+        <v>1105.4692</v>
       </c>
       <c r="W3" t="n">
-        <v>9.3636</v>
+        <v>9.0909</v>
       </c>
       <c r="X3" t="n">
-        <v>13.2727</v>
+        <v>13</v>
       </c>
       <c r="Y3" t="n">
-        <v>14.8182</v>
+        <v>15</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.03838905</v>
+        <v>0.03846082</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.03399229</v>
+        <v>0.0338477</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -800,22 +800,22 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>6.1251</v>
+        <v>7.3706</v>
       </c>
       <c r="AE3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF3" t="n">
         <v>4</v>
       </c>
       <c r="AG3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AH3" t="n">
-        <v>32892</v>
+        <v>32773</v>
       </c>
       <c r="AI3" t="n">
-        <v>5.5062</v>
+        <v>6.5261</v>
       </c>
     </row>
     <row r="4">
@@ -844,16 +844,16 @@
         <v>2066</v>
       </c>
       <c r="G4" t="n">
-        <v>7.5833</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>306.5833</v>
+        <v>246.0833</v>
       </c>
       <c r="I4" t="n">
-        <v>966.4167</v>
+        <v>792.5</v>
       </c>
       <c r="J4" t="n">
-        <v>0.04470139</v>
+        <v>0.03420484</v>
       </c>
       <c r="K4" t="n">
         <v>222.1007</v>
@@ -871,40 +871,40 @@
         <v>0.9814000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.03474981</v>
+        <v>0.02777727</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04342795</v>
+        <v>0.03565817</v>
       </c>
       <c r="R4" t="n">
-        <v>3.3871</v>
+        <v>2.6944</v>
       </c>
       <c r="S4" t="n">
-        <v>232.5</v>
+        <v>193.6667</v>
       </c>
       <c r="T4" t="n">
-        <v>572.8333</v>
+        <v>582.6667</v>
       </c>
       <c r="U4" t="n">
-        <v>342.9959</v>
+        <v>275.1036</v>
       </c>
       <c r="V4" t="n">
-        <v>1096.3385</v>
+        <v>904.0088</v>
       </c>
       <c r="W4" t="n">
-        <v>8.583299999999999</v>
+        <v>6.4167</v>
       </c>
       <c r="X4" t="n">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>14.5833</v>
+        <v>11.4167</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.05068186</v>
+        <v>0.03894283</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.04470139</v>
+        <v>0.03420484</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -912,22 +912,22 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>5.818</v>
+        <v>7.0396</v>
       </c>
       <c r="AE4" t="n">
-        <v>6</v>
+        <v>7.2111</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.8284</v>
+        <v>4</v>
       </c>
       <c r="AG4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AH4" t="n">
-        <v>45758</v>
+        <v>35034</v>
       </c>
       <c r="AI4" t="n">
-        <v>4.9642</v>
+        <v>6.2875</v>
       </c>
     </row>
     <row r="5">
@@ -956,16 +956,16 @@
         <v>2174</v>
       </c>
       <c r="G5" t="n">
-        <v>6.8889</v>
+        <v>6.6667</v>
       </c>
       <c r="H5" t="n">
-        <v>313.5556</v>
+        <v>270.7778</v>
       </c>
       <c r="I5" t="n">
-        <v>989.8889</v>
+        <v>847.2222</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04513983</v>
+        <v>0.03452098</v>
       </c>
       <c r="K5" t="n">
         <v>236.3819</v>
@@ -983,40 +983,40 @@
         <v>0.9957</v>
       </c>
       <c r="P5" t="n">
-        <v>0.03428217</v>
+        <v>0.02932336</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.04317158</v>
+        <v>0.03663061</v>
       </c>
       <c r="R5" t="n">
-        <v>2.9693</v>
+        <v>2.8471</v>
       </c>
       <c r="S5" t="n">
-        <v>220.8889</v>
+        <v>203</v>
       </c>
       <c r="T5" t="n">
-        <v>507.3333</v>
+        <v>540.5556</v>
       </c>
       <c r="U5" t="n">
-        <v>351.7792</v>
+        <v>306.6534</v>
       </c>
       <c r="V5" t="n">
-        <v>1119.6164</v>
+        <v>964.4395</v>
       </c>
       <c r="W5" t="n">
-        <v>7.7778</v>
+        <v>6.4444</v>
       </c>
       <c r="X5" t="n">
+        <v>10.7778</v>
+      </c>
+      <c r="Y5" t="n">
         <v>13.2222</v>
       </c>
-      <c r="Y5" t="n">
-        <v>16</v>
-      </c>
       <c r="Z5" t="n">
-        <v>0.05110365</v>
+        <v>0.03927722</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.04513983</v>
+        <v>0.03452098</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -1024,22 +1024,22 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>5.7797</v>
+        <v>7.0431</v>
       </c>
       <c r="AE5" t="n">
-        <v>6</v>
+        <v>7.2111</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.8284</v>
+        <v>4</v>
       </c>
       <c r="AG5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AH5" t="n">
-        <v>46400</v>
+        <v>35500</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.0947</v>
+        <v>6.4086</v>
       </c>
     </row>
     <row r="6">
@@ -1068,16 +1068,16 @@
         <v>1736</v>
       </c>
       <c r="G6" t="n">
-        <v>6.7273</v>
+        <v>5.7273</v>
       </c>
       <c r="H6" t="n">
-        <v>302.9091</v>
+        <v>274.0909</v>
       </c>
       <c r="I6" t="n">
-        <v>961.3636</v>
+        <v>830.1818</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04380241</v>
+        <v>0.0356981</v>
       </c>
       <c r="K6" t="n">
         <v>207.4787</v>
@@ -1095,40 +1095,40 @@
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03624067</v>
+        <v>0.03303183</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.04402843</v>
+        <v>0.03811779</v>
       </c>
       <c r="R6" t="n">
-        <v>3.2312</v>
+        <v>2.8038</v>
       </c>
       <c r="S6" t="n">
-        <v>204.6364</v>
+        <v>205.4545</v>
       </c>
       <c r="T6" t="n">
-        <v>498.3636</v>
+        <v>516.4545000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>341.9271</v>
+        <v>310.7516</v>
       </c>
       <c r="V6" t="n">
-        <v>1087.2355</v>
+        <v>939.5478000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>8.0909</v>
+        <v>6.5455</v>
       </c>
       <c r="X6" t="n">
-        <v>11.7273</v>
+        <v>10.0909</v>
       </c>
       <c r="Y6" t="n">
-        <v>14.2727</v>
+        <v>12.4545</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.04958231</v>
+        <v>0.04054955</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.04380241</v>
+        <v>0.0356981</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -1136,22 +1136,22 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>5.7808</v>
+        <v>6.908</v>
       </c>
       <c r="AE6" t="n">
-        <v>6</v>
+        <v>7.2111</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.8284</v>
+        <v>4</v>
       </c>
       <c r="AG6" t="n">
-        <v>8</v>
+        <v>8.9443</v>
       </c>
       <c r="AH6" t="n">
-        <v>45013</v>
+        <v>36701</v>
       </c>
       <c r="AI6" t="n">
-        <v>4.9871</v>
+        <v>6.0179</v>
       </c>
     </row>
     <row r="7">
@@ -1180,16 +1180,16 @@
         <v>2671.5</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="H7" t="n">
-        <v>396.75</v>
+        <v>422.875</v>
       </c>
       <c r="I7" t="n">
-        <v>982</v>
+        <v>1024.375</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03464652</v>
+        <v>0.03219148</v>
       </c>
       <c r="K7" t="n">
         <v>275.4257</v>
@@ -1207,40 +1207,40 @@
         <v>0.9949</v>
       </c>
       <c r="P7" t="n">
-        <v>0.03800643</v>
+        <v>0.04052149</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.04004776</v>
+        <v>0.0416417</v>
       </c>
       <c r="R7" t="n">
-        <v>3.538</v>
+        <v>3.7643</v>
       </c>
       <c r="S7" t="n">
-        <v>317.125</v>
+        <v>351.625</v>
       </c>
       <c r="T7" t="n">
-        <v>673.25</v>
+        <v>809.5</v>
       </c>
       <c r="U7" t="n">
-        <v>445.9204</v>
+        <v>477.0898</v>
       </c>
       <c r="V7" t="n">
-        <v>1103.9582</v>
+        <v>1157.942</v>
       </c>
       <c r="W7" t="n">
-        <v>10.75</v>
+        <v>10.875</v>
       </c>
       <c r="X7" t="n">
-        <v>14.25</v>
+        <v>14</v>
       </c>
       <c r="Y7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03869506</v>
+        <v>0.03621496</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.03502703</v>
+        <v>0.03353699</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -1248,22 +1248,22 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>5.7755</v>
+        <v>6.7319</v>
       </c>
       <c r="AE7" t="n">
-        <v>6</v>
+        <v>7.2111</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.8284</v>
+        <v>4</v>
       </c>
       <c r="AG7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>32998</v>
+        <v>31623</v>
       </c>
       <c r="AI7" t="n">
-        <v>5.5385</v>
+        <v>6.2246</v>
       </c>
     </row>
     <row r="8">
@@ -1292,16 +1292,16 @@
         <v>1519</v>
       </c>
       <c r="G8" t="n">
-        <v>6.7273</v>
+        <v>6.6364</v>
       </c>
       <c r="H8" t="n">
-        <v>283.3636</v>
+        <v>300.0909</v>
       </c>
       <c r="I8" t="n">
-        <v>795.1818</v>
+        <v>819.1818</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03829817</v>
+        <v>0.03344539</v>
       </c>
       <c r="K8" t="n">
         <v>221.5717</v>
@@ -1319,40 +1319,40 @@
         <v>0.9972</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03201806</v>
+        <v>0.03400888</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0356529</v>
+        <v>0.0367476</v>
       </c>
       <c r="R8" t="n">
-        <v>3.0793</v>
+        <v>3.0582</v>
       </c>
       <c r="S8" t="n">
-        <v>213.2727</v>
+        <v>238.4545</v>
       </c>
       <c r="T8" t="n">
-        <v>419.4545</v>
+        <v>519.5454999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>315.3412</v>
+        <v>337.4499</v>
       </c>
       <c r="V8" t="n">
-        <v>890.9974</v>
+        <v>924.8247</v>
       </c>
       <c r="W8" t="n">
-        <v>7.4545</v>
+        <v>7.5455</v>
       </c>
       <c r="X8" t="n">
-        <v>10.8182</v>
+        <v>10.7273</v>
       </c>
       <c r="Y8" t="n">
-        <v>13</v>
+        <v>12.4545</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.04303411</v>
+        <v>0.03785717</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.0380563</v>
+        <v>0.034249</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -1360,22 +1360,22 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>5.8663</v>
+        <v>6.9427</v>
       </c>
       <c r="AE8" t="n">
-        <v>6</v>
+        <v>7.2111</v>
       </c>
       <c r="AF8" t="n">
         <v>4</v>
       </c>
       <c r="AG8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AH8" t="n">
-        <v>36498</v>
+        <v>32870</v>
       </c>
       <c r="AI8" t="n">
-        <v>5.2823</v>
+        <v>6.2512</v>
       </c>
     </row>
     <row r="9">
@@ -1404,16 +1404,16 @@
         <v>1624</v>
       </c>
       <c r="G9" t="n">
-        <v>5.5455</v>
+        <v>5.3636</v>
       </c>
       <c r="H9" t="n">
-        <v>250.2727</v>
+        <v>250.4545</v>
       </c>
       <c r="I9" t="n">
-        <v>697.4545000000001</v>
+        <v>647.0909</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03748464</v>
+        <v>0.02865668</v>
       </c>
       <c r="K9" t="n">
         <v>201.3086</v>
@@ -1431,40 +1431,40 @@
         <v>0.981</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03152782</v>
+        <v>0.0313798</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03455861</v>
+        <v>0.03234375</v>
       </c>
       <c r="R9" t="n">
-        <v>2.8431</v>
+        <v>2.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>177.2727</v>
+        <v>186.9091</v>
       </c>
       <c r="T9" t="n">
-        <v>349.3636</v>
+        <v>401.6364</v>
       </c>
       <c r="U9" t="n">
-        <v>277.0839</v>
+        <v>277.945</v>
       </c>
       <c r="V9" t="n">
-        <v>775.4374</v>
+        <v>723.2128</v>
       </c>
       <c r="W9" t="n">
         <v>6.2727</v>
       </c>
       <c r="X9" t="n">
-        <v>9.454499999999999</v>
+        <v>9.2727</v>
       </c>
       <c r="Y9" t="n">
-        <v>11.4545</v>
+        <v>10.2727</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.04198674</v>
+        <v>0.03240016</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03688309</v>
+        <v>0.02970713</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -1472,22 +1472,22 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>5.7908</v>
+        <v>6.7771</v>
       </c>
       <c r="AE9" t="n">
-        <v>6</v>
+        <v>7.2111</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.8284</v>
+        <v>4</v>
       </c>
       <c r="AG9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AH9" t="n">
-        <v>34940</v>
+        <v>28159</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.0813</v>
+        <v>5.9497</v>
       </c>
     </row>
   </sheetData>
@@ -1584,7 +1584,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>length on lacuna size (docs/OVERNIGHT_REPORT.md, task 4.1).</t>
+          <t>length on lacuna size (the overnight report, tag archive-2026-10-13, task 4.1).</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>docs/CANALICULI_V2_REPORT.md.</t>
+          <t>the canaliculi v2 report, tag archive-2026-10-13.</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Measured only on skeleton pixels with real signal under them: bridged pixels, the lacuna buffer and the</t>
+          <t>Measured only on skeleton pixels on the canalicular mask: the lacuna buffer and the</t>
         </is>
       </c>
     </row>

--- a/results/all_images/quantification/quantification_all_images.xlsx
+++ b/results/all_images/quantification/quantification_all_images.xlsx
@@ -611,76 +611,76 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" t="n">
         <v>3013</v>
       </c>
       <c r="G2" t="n">
-        <v>10.9231</v>
+        <v>11</v>
       </c>
       <c r="H2" t="n">
-        <v>422.0769</v>
+        <v>433.1429</v>
       </c>
       <c r="I2" t="n">
-        <v>1022.4615</v>
+        <v>995.9286</v>
       </c>
       <c r="J2" t="n">
-        <v>0.037413</v>
+        <v>0.03891869</v>
       </c>
       <c r="K2" t="n">
-        <v>297.8123</v>
+        <v>280.6021</v>
       </c>
       <c r="L2" t="n">
-        <v>10771.6923</v>
+        <v>10209.4286</v>
       </c>
       <c r="M2" t="n">
-        <v>25565.4615</v>
+        <v>23888.4286</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9908</v>
+        <v>0.9913999999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>0.03830376</v>
+        <v>0.04140095</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.03934038</v>
+        <v>0.04048473</v>
       </c>
       <c r="R2" t="n">
-        <v>3.7216</v>
+        <v>4.0757</v>
       </c>
       <c r="S2" t="n">
-        <v>356.4615</v>
+        <v>379.2857</v>
       </c>
       <c r="T2" t="n">
-        <v>745.8462</v>
+        <v>789</v>
       </c>
       <c r="U2" t="n">
-        <v>478.7993</v>
+        <v>492.1853</v>
       </c>
       <c r="V2" t="n">
-        <v>1157.4735</v>
+        <v>1128.49</v>
       </c>
       <c r="W2" t="n">
-        <v>9.461499999999999</v>
+        <v>9.357100000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>13.4615</v>
+        <v>13.1429</v>
       </c>
       <c r="Y2" t="n">
-        <v>14.0769</v>
+        <v>13.2143</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.04234794</v>
+        <v>0.04408455</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.03737811</v>
+        <v>0.03886559</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -688,22 +688,22 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>7.3668</v>
+        <v>8.154500000000001</v>
       </c>
       <c r="AE2" t="n">
-        <v>8</v>
+        <v>8.2462</v>
       </c>
       <c r="AF2" t="n">
-        <v>4</v>
+        <v>5.6569</v>
       </c>
       <c r="AG2" t="n">
-        <v>10</v>
+        <v>10.7703</v>
       </c>
       <c r="AH2" t="n">
-        <v>36570</v>
+        <v>38017</v>
       </c>
       <c r="AI2" t="n">
-        <v>6.6809</v>
+        <v>7.4897</v>
       </c>
     </row>
     <row r="3">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
         <v>11</v>
@@ -732,25 +732,25 @@
         <v>3684</v>
       </c>
       <c r="G3" t="n">
-        <v>8.2727</v>
+        <v>6.1818</v>
       </c>
       <c r="H3" t="n">
-        <v>371.6364</v>
+        <v>399.2727</v>
       </c>
       <c r="I3" t="n">
-        <v>978.9091</v>
+        <v>1055.1818</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03400824</v>
+        <v>0.03641101</v>
       </c>
       <c r="K3" t="n">
         <v>349.6878</v>
       </c>
       <c r="L3" t="n">
-        <v>12006.1818</v>
+        <v>11901.1818</v>
       </c>
       <c r="M3" t="n">
-        <v>28554.2727</v>
+        <v>28359.3636</v>
       </c>
       <c r="N3" t="n">
         <v>0.9834000000000001</v>
@@ -759,40 +759,40 @@
         <v>0.9555</v>
       </c>
       <c r="P3" t="n">
-        <v>0.03007332</v>
+        <v>0.03273455</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03369617</v>
+        <v>0.03657206</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4334</v>
+        <v>1.6497</v>
       </c>
       <c r="S3" t="n">
-        <v>286.7273</v>
+        <v>314.9091</v>
       </c>
       <c r="T3" t="n">
-        <v>664.3636</v>
+        <v>786</v>
       </c>
       <c r="U3" t="n">
-        <v>414.3253</v>
+        <v>444.7003</v>
       </c>
       <c r="V3" t="n">
-        <v>1105.4692</v>
+        <v>1189.7529</v>
       </c>
       <c r="W3" t="n">
-        <v>9.0909</v>
+        <v>9.545500000000001</v>
       </c>
       <c r="X3" t="n">
-        <v>13</v>
+        <v>14.1818</v>
       </c>
       <c r="Y3" t="n">
-        <v>15</v>
+        <v>15.8182</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.03846082</v>
+        <v>0.04114015</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0338477</v>
+        <v>0.03634245</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -800,22 +800,22 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>7.3706</v>
+        <v>8.0998</v>
       </c>
       <c r="AE3" t="n">
-        <v>8</v>
+        <v>8.2462</v>
       </c>
       <c r="AF3" t="n">
-        <v>4</v>
+        <v>4.4721</v>
       </c>
       <c r="AG3" t="n">
-        <v>10</v>
+        <v>10.7703</v>
       </c>
       <c r="AH3" t="n">
-        <v>32773</v>
+        <v>35180</v>
       </c>
       <c r="AI3" t="n">
-        <v>6.5261</v>
+        <v>7.355</v>
       </c>
     </row>
     <row r="4">
@@ -844,16 +844,16 @@
         <v>2066</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>3.5833</v>
       </c>
       <c r="H4" t="n">
-        <v>246.0833</v>
+        <v>272.1667</v>
       </c>
       <c r="I4" t="n">
-        <v>792.5</v>
+        <v>859.1667</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03420484</v>
+        <v>0.03689268</v>
       </c>
       <c r="K4" t="n">
         <v>222.1007</v>
@@ -871,40 +871,40 @@
         <v>0.9814000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.02777727</v>
+        <v>0.0309508</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03565817</v>
+        <v>0.03889819</v>
       </c>
       <c r="R4" t="n">
-        <v>2.6944</v>
+        <v>1.5461</v>
       </c>
       <c r="S4" t="n">
-        <v>193.6667</v>
+        <v>220</v>
       </c>
       <c r="T4" t="n">
-        <v>582.6667</v>
+        <v>642.75</v>
       </c>
       <c r="U4" t="n">
-        <v>275.1036</v>
+        <v>306.1293</v>
       </c>
       <c r="V4" t="n">
-        <v>904.0088</v>
+        <v>981.0484</v>
       </c>
       <c r="W4" t="n">
-        <v>6.4167</v>
+        <v>7.1667</v>
       </c>
       <c r="X4" t="n">
-        <v>9.5</v>
+        <v>9.916700000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>11.4167</v>
+        <v>12.3333</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.03894283</v>
+        <v>0.04200993</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03420484</v>
+        <v>0.03689268</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -912,22 +912,22 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>7.0396</v>
+        <v>7.8995</v>
       </c>
       <c r="AE4" t="n">
-        <v>7.2111</v>
+        <v>8</v>
       </c>
       <c r="AF4" t="n">
-        <v>4</v>
+        <v>4.4721</v>
       </c>
       <c r="AG4" t="n">
-        <v>10</v>
+        <v>10.198</v>
       </c>
       <c r="AH4" t="n">
-        <v>35034</v>
+        <v>37787</v>
       </c>
       <c r="AI4" t="n">
-        <v>6.2875</v>
+        <v>7.346</v>
       </c>
     </row>
     <row r="5">
@@ -947,76 +947,76 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>11</v>
+      </c>
+      <c r="E5" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="n">
-        <v>9</v>
-      </c>
       <c r="F5" t="n">
-        <v>2174</v>
+        <v>2188.5</v>
       </c>
       <c r="G5" t="n">
-        <v>6.6667</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>270.7778</v>
+        <v>283.2</v>
       </c>
       <c r="I5" t="n">
-        <v>847.2222</v>
+        <v>841.7</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03452098</v>
+        <v>0.03476499</v>
       </c>
       <c r="K5" t="n">
-        <v>236.3819</v>
+        <v>254.3427</v>
       </c>
       <c r="L5" t="n">
-        <v>9046.2222</v>
+        <v>9495.200000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>22951.3333</v>
+        <v>23331.5</v>
       </c>
       <c r="N5" t="n">
-        <v>1</v>
+        <v>0.9969</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9957</v>
+        <v>0.9761</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02932336</v>
+        <v>0.02907057</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03663061</v>
+        <v>0.03556791</v>
       </c>
       <c r="R5" t="n">
-        <v>2.8471</v>
+        <v>1.0675</v>
       </c>
       <c r="S5" t="n">
-        <v>203</v>
+        <v>224.3</v>
       </c>
       <c r="T5" t="n">
-        <v>540.5556</v>
+        <v>566.8</v>
       </c>
       <c r="U5" t="n">
-        <v>306.6534</v>
+        <v>319.4545</v>
       </c>
       <c r="V5" t="n">
-        <v>964.4395</v>
+        <v>956.5041</v>
       </c>
       <c r="W5" t="n">
-        <v>6.4444</v>
+        <v>6.9</v>
       </c>
       <c r="X5" t="n">
-        <v>10.7778</v>
+        <v>10.7</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.2222</v>
+        <v>11.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03927722</v>
+        <v>0.03958983</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.03452098</v>
+        <v>0.03476499</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -1024,22 +1024,22 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>7.0431</v>
+        <v>7.7028</v>
       </c>
       <c r="AE5" t="n">
-        <v>7.2111</v>
+        <v>8</v>
       </c>
       <c r="AF5" t="n">
-        <v>4</v>
+        <v>4.4721</v>
       </c>
       <c r="AG5" t="n">
         <v>10</v>
       </c>
       <c r="AH5" t="n">
-        <v>35500</v>
+        <v>35628</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.4086</v>
+        <v>7.238</v>
       </c>
     </row>
     <row r="6">
@@ -1068,16 +1068,16 @@
         <v>1736</v>
       </c>
       <c r="G6" t="n">
-        <v>5.7273</v>
+        <v>4.3636</v>
       </c>
       <c r="H6" t="n">
-        <v>274.0909</v>
+        <v>310.3636</v>
       </c>
       <c r="I6" t="n">
-        <v>830.1818</v>
+        <v>922.8182</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0356981</v>
+        <v>0.04023368</v>
       </c>
       <c r="K6" t="n">
         <v>207.4787</v>
@@ -1095,40 +1095,40 @@
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03303183</v>
+        <v>0.03743945</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03811779</v>
+        <v>0.042466</v>
       </c>
       <c r="R6" t="n">
-        <v>2.8038</v>
+        <v>2.1027</v>
       </c>
       <c r="S6" t="n">
-        <v>205.4545</v>
+        <v>244.9091</v>
       </c>
       <c r="T6" t="n">
-        <v>516.4545000000001</v>
+        <v>657.9091</v>
       </c>
       <c r="U6" t="n">
-        <v>310.7516</v>
+        <v>352.2418</v>
       </c>
       <c r="V6" t="n">
-        <v>939.5478000000001</v>
+        <v>1046.4873</v>
       </c>
       <c r="W6" t="n">
-        <v>6.5455</v>
+        <v>6.8182</v>
       </c>
       <c r="X6" t="n">
-        <v>10.0909</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.4545</v>
+        <v>13.4545</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.04054955</v>
+        <v>0.04570415</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0356981</v>
+        <v>0.04023368</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -1136,22 +1136,22 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>6.908</v>
+        <v>7.6176</v>
       </c>
       <c r="AE6" t="n">
-        <v>7.2111</v>
+        <v>8</v>
       </c>
       <c r="AF6" t="n">
-        <v>4</v>
+        <v>4.4721</v>
       </c>
       <c r="AG6" t="n">
-        <v>8.9443</v>
+        <v>10</v>
       </c>
       <c r="AH6" t="n">
-        <v>36701</v>
+        <v>41364</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.0179</v>
+        <v>7.0667</v>
       </c>
     </row>
     <row r="7">
@@ -1180,16 +1180,16 @@
         <v>2671.5</v>
       </c>
       <c r="G7" t="n">
-        <v>10.5</v>
+        <v>8.875</v>
       </c>
       <c r="H7" t="n">
-        <v>422.875</v>
+        <v>460</v>
       </c>
       <c r="I7" t="n">
-        <v>1024.375</v>
+        <v>1083.375</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03219148</v>
+        <v>0.03446477</v>
       </c>
       <c r="K7" t="n">
         <v>275.4257</v>
@@ -1207,40 +1207,40 @@
         <v>0.9949</v>
       </c>
       <c r="P7" t="n">
-        <v>0.04052149</v>
+        <v>0.0440793</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0416417</v>
+        <v>0.04405889</v>
       </c>
       <c r="R7" t="n">
-        <v>3.7643</v>
+        <v>3.2531</v>
       </c>
       <c r="S7" t="n">
-        <v>351.625</v>
+        <v>397.75</v>
       </c>
       <c r="T7" t="n">
-        <v>809.5</v>
+        <v>902.875</v>
       </c>
       <c r="U7" t="n">
-        <v>477.0898</v>
+        <v>520.8569</v>
       </c>
       <c r="V7" t="n">
-        <v>1157.942</v>
+        <v>1226.0753</v>
       </c>
       <c r="W7" t="n">
         <v>10.875</v>
       </c>
       <c r="X7" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>16.5</v>
+        <v>16.25</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03621496</v>
+        <v>0.03880481</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.03353699</v>
+        <v>0.03544169</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -1248,10 +1248,10 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>6.7319</v>
+        <v>7.5376</v>
       </c>
       <c r="AE7" t="n">
-        <v>7.2111</v>
+        <v>8</v>
       </c>
       <c r="AF7" t="n">
         <v>4</v>
@@ -1260,10 +1260,10 @@
         <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>31623</v>
+        <v>33419</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.2246</v>
+        <v>7.1884</v>
       </c>
     </row>
     <row r="8">
@@ -1292,16 +1292,16 @@
         <v>1519</v>
       </c>
       <c r="G8" t="n">
-        <v>6.6364</v>
+        <v>5.9091</v>
       </c>
       <c r="H8" t="n">
-        <v>300.0909</v>
+        <v>315.1818</v>
       </c>
       <c r="I8" t="n">
-        <v>819.1818</v>
+        <v>864.1818</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03344539</v>
+        <v>0.03524355</v>
       </c>
       <c r="K8" t="n">
         <v>221.5717</v>
@@ -1319,25 +1319,25 @@
         <v>0.9972</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03400888</v>
+        <v>0.03580719</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0367476</v>
+        <v>0.03881081</v>
       </c>
       <c r="R8" t="n">
-        <v>3.0582</v>
+        <v>2.7497</v>
       </c>
       <c r="S8" t="n">
-        <v>238.4545</v>
+        <v>256.9091</v>
       </c>
       <c r="T8" t="n">
-        <v>519.5454999999999</v>
+        <v>596.4545000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>337.4499</v>
+        <v>356.2859</v>
       </c>
       <c r="V8" t="n">
-        <v>924.8247</v>
+        <v>975.7318</v>
       </c>
       <c r="W8" t="n">
         <v>7.5455</v>
@@ -1346,13 +1346,13 @@
         <v>10.7273</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.4545</v>
+        <v>12.7273</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03785717</v>
+        <v>0.03988112</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.034249</v>
+        <v>0.03614952</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -1360,22 +1360,22 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>6.9427</v>
+        <v>7.7083</v>
       </c>
       <c r="AE8" t="n">
-        <v>7.2111</v>
+        <v>8</v>
       </c>
       <c r="AF8" t="n">
         <v>4</v>
       </c>
       <c r="AG8" t="n">
-        <v>10</v>
+        <v>10.198</v>
       </c>
       <c r="AH8" t="n">
-        <v>32870</v>
+        <v>34694</v>
       </c>
       <c r="AI8" t="n">
-        <v>6.2512</v>
+        <v>7.1227</v>
       </c>
     </row>
     <row r="9">
@@ -1395,76 +1395,76 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F9" t="n">
         <v>1624</v>
       </c>
       <c r="G9" t="n">
-        <v>5.3636</v>
+        <v>5.3333</v>
       </c>
       <c r="H9" t="n">
-        <v>250.4545</v>
+        <v>271.3333</v>
       </c>
       <c r="I9" t="n">
-        <v>647.0909</v>
+        <v>719.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0.02865668</v>
+        <v>0.03274213</v>
       </c>
       <c r="K9" t="n">
-        <v>201.3086</v>
+        <v>188.4875</v>
       </c>
       <c r="L9" t="n">
-        <v>7938.5455</v>
+        <v>7625.9167</v>
       </c>
       <c r="M9" t="n">
-        <v>19815</v>
+        <v>19043.3333</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9943</v>
+        <v>0.9948</v>
       </c>
       <c r="O9" t="n">
-        <v>0.981</v>
+        <v>0.9826</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0313798</v>
+        <v>0.03567298</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03234375</v>
+        <v>0.03762232</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7581</v>
+        <v>2.8718</v>
       </c>
       <c r="S9" t="n">
-        <v>186.9091</v>
+        <v>202.1667</v>
       </c>
       <c r="T9" t="n">
-        <v>401.6364</v>
+        <v>470.0833</v>
       </c>
       <c r="U9" t="n">
-        <v>277.945</v>
+        <v>302.0262</v>
       </c>
       <c r="V9" t="n">
-        <v>723.2128</v>
+        <v>805.3094</v>
       </c>
       <c r="W9" t="n">
-        <v>6.2727</v>
+        <v>6</v>
       </c>
       <c r="X9" t="n">
-        <v>9.2727</v>
+        <v>9.333299999999999</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.2727</v>
+        <v>11.1667</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03240016</v>
+        <v>0.03700763</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02970713</v>
+        <v>0.03305751</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>6.7771</v>
+        <v>7.4342</v>
       </c>
       <c r="AE9" t="n">
-        <v>7.2111</v>
+        <v>8</v>
       </c>
       <c r="AF9" t="n">
         <v>4</v>
@@ -1484,10 +1484,10 @@
         <v>10</v>
       </c>
       <c r="AH9" t="n">
-        <v>28159</v>
+        <v>31329</v>
       </c>
       <c r="AI9" t="n">
-        <v>5.9497</v>
+        <v>6.9667</v>
       </c>
     </row>
   </sheetData>

--- a/results/all_images/quantification/quantification_all_images.xlsx
+++ b/results/all_images/quantification/quantification_all_images.xlsx
@@ -611,76 +611,76 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" t="n">
         <v>3013</v>
       </c>
       <c r="G2" t="n">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="H2" t="n">
-        <v>433.1429</v>
+        <v>447.6667</v>
       </c>
       <c r="I2" t="n">
-        <v>995.9286</v>
+        <v>1016.0667</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03891869</v>
+        <v>0.03897445</v>
       </c>
       <c r="K2" t="n">
-        <v>280.6021</v>
+        <v>292.0698</v>
       </c>
       <c r="L2" t="n">
-        <v>10209.4286</v>
+        <v>10491.4667</v>
       </c>
       <c r="M2" t="n">
-        <v>23888.4286</v>
+        <v>24400.8667</v>
       </c>
       <c r="N2" t="n">
         <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9913999999999999</v>
+        <v>0.9858</v>
       </c>
       <c r="P2" t="n">
-        <v>0.04140095</v>
+        <v>0.04176754</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.04048473</v>
+        <v>0.04050161</v>
       </c>
       <c r="R2" t="n">
-        <v>4.0757</v>
+        <v>4.05</v>
       </c>
       <c r="S2" t="n">
-        <v>379.2857</v>
+        <v>392.8667</v>
       </c>
       <c r="T2" t="n">
-        <v>789</v>
+        <v>810.2</v>
       </c>
       <c r="U2" t="n">
-        <v>492.1853</v>
+        <v>509.1242</v>
       </c>
       <c r="V2" t="n">
-        <v>1128.49</v>
+        <v>1153.1702</v>
       </c>
       <c r="W2" t="n">
-        <v>9.357100000000001</v>
+        <v>9.6</v>
       </c>
       <c r="X2" t="n">
-        <v>13.1429</v>
+        <v>13.2667</v>
       </c>
       <c r="Y2" t="n">
-        <v>13.2143</v>
+        <v>13.8667</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.04408455</v>
+        <v>0.0441484</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.03886559</v>
+        <v>0.03892297</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -688,22 +688,22 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>8.154500000000001</v>
+        <v>8.1572</v>
       </c>
       <c r="AE2" t="n">
         <v>8.2462</v>
       </c>
       <c r="AF2" t="n">
-        <v>5.6569</v>
+        <v>4.4721</v>
       </c>
       <c r="AG2" t="n">
         <v>10.7703</v>
       </c>
       <c r="AH2" t="n">
-        <v>38017</v>
+        <v>37978</v>
       </c>
       <c r="AI2" t="n">
-        <v>7.4897</v>
+        <v>7.5373</v>
       </c>
     </row>
     <row r="3">
@@ -947,76 +947,76 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F5" t="n">
         <v>2188.5</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="H5" t="n">
-        <v>283.2</v>
+        <v>242.3333</v>
       </c>
       <c r="I5" t="n">
-        <v>841.7</v>
+        <v>762.25</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03476499</v>
+        <v>0.03476352</v>
       </c>
       <c r="K5" t="n">
-        <v>254.3427</v>
+        <v>221.0149</v>
       </c>
       <c r="L5" t="n">
-        <v>9495.200000000001</v>
+        <v>8668.5</v>
       </c>
       <c r="M5" t="n">
-        <v>23331.5</v>
+        <v>21815.6667</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9969</v>
+        <v>0.9974</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9761</v>
+        <v>0.9801</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02907057</v>
+        <v>0.02560946</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03556791</v>
+        <v>0.03384685</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0675</v>
+        <v>0.8924</v>
       </c>
       <c r="S5" t="n">
-        <v>224.3</v>
+        <v>187.5833</v>
       </c>
       <c r="T5" t="n">
-        <v>566.8</v>
+        <v>476.1667</v>
       </c>
       <c r="U5" t="n">
-        <v>319.4545</v>
+        <v>273.5523</v>
       </c>
       <c r="V5" t="n">
-        <v>956.5041</v>
+        <v>867.2576</v>
       </c>
       <c r="W5" t="n">
-        <v>6.9</v>
+        <v>5.8333</v>
       </c>
       <c r="X5" t="n">
-        <v>10.7</v>
+        <v>9.333299999999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.8</v>
+        <v>10.4167</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03958983</v>
+        <v>0.03959204</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.03476499</v>
+        <v>0.03476352</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>7.7028</v>
+        <v>7.7041</v>
       </c>
       <c r="AE5" t="n">
         <v>8</v>
@@ -1036,10 +1036,10 @@
         <v>10</v>
       </c>
       <c r="AH5" t="n">
-        <v>35628</v>
+        <v>35600</v>
       </c>
       <c r="AI5" t="n">
-        <v>7.238</v>
+        <v>6.8669</v>
       </c>
     </row>
     <row r="6">
@@ -1171,76 +1171,76 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="n">
         <v>2671.5</v>
       </c>
       <c r="G7" t="n">
-        <v>8.875</v>
+        <v>8.333299999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>460</v>
+        <v>415</v>
       </c>
       <c r="I7" t="n">
-        <v>1083.375</v>
+        <v>979.3333</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03446477</v>
+        <v>0.03447141</v>
       </c>
       <c r="K7" t="n">
-        <v>275.4257</v>
+        <v>253.4606</v>
       </c>
       <c r="L7" t="n">
-        <v>10379.625</v>
+        <v>9783.3333</v>
       </c>
       <c r="M7" t="n">
-        <v>24427.5</v>
+        <v>23226.1111</v>
       </c>
       <c r="N7" t="n">
         <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9949</v>
+        <v>0.9809</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0440793</v>
+        <v>0.04040066</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.04405889</v>
+        <v>0.04036312</v>
       </c>
       <c r="R7" t="n">
-        <v>3.2531</v>
+        <v>3.4633</v>
       </c>
       <c r="S7" t="n">
-        <v>397.75</v>
+        <v>359.1111</v>
       </c>
       <c r="T7" t="n">
-        <v>902.875</v>
+        <v>808.1111</v>
       </c>
       <c r="U7" t="n">
-        <v>520.8569</v>
+        <v>469.7742</v>
       </c>
       <c r="V7" t="n">
-        <v>1226.0753</v>
+        <v>1107.8014</v>
       </c>
       <c r="W7" t="n">
-        <v>10.875</v>
+        <v>9.777799999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Y7" t="n">
-        <v>16.25</v>
+        <v>14.5556</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03880481</v>
+        <v>0.03880816</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.03544169</v>
+        <v>0.03544909</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>7.5376</v>
+        <v>7.5333</v>
       </c>
       <c r="AE7" t="n">
         <v>8</v>
@@ -1260,10 +1260,10 @@
         <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>33419</v>
+        <v>33418</v>
       </c>
       <c r="AI7" t="n">
-        <v>7.1884</v>
+        <v>6.9508</v>
       </c>
     </row>
     <row r="8">
@@ -1395,76 +1395,76 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9" t="n">
-        <v>1624</v>
+        <v>1511.5</v>
       </c>
       <c r="G9" t="n">
-        <v>5.3333</v>
+        <v>5.4615</v>
       </c>
       <c r="H9" t="n">
-        <v>271.3333</v>
+        <v>263.9231</v>
       </c>
       <c r="I9" t="n">
-        <v>719.5</v>
+        <v>707</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03274213</v>
+        <v>0.03282691</v>
       </c>
       <c r="K9" t="n">
-        <v>188.4875</v>
+        <v>186.0541</v>
       </c>
       <c r="L9" t="n">
-        <v>7625.9167</v>
+        <v>7571.7692</v>
       </c>
       <c r="M9" t="n">
-        <v>19043.3333</v>
+        <v>19073</v>
       </c>
       <c r="N9" t="n">
-        <v>0.9948</v>
+        <v>0.9952</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9826</v>
+        <v>0.9839</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03567298</v>
+        <v>0.03487364</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03762232</v>
+        <v>0.03693351</v>
       </c>
       <c r="R9" t="n">
-        <v>2.8718</v>
+        <v>2.9942</v>
       </c>
       <c r="S9" t="n">
-        <v>202.1667</v>
+        <v>198.8462</v>
       </c>
       <c r="T9" t="n">
-        <v>470.0833</v>
+        <v>463</v>
       </c>
       <c r="U9" t="n">
-        <v>302.0262</v>
+        <v>294.7215</v>
       </c>
       <c r="V9" t="n">
-        <v>805.3094</v>
+        <v>793.1523999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>6</v>
+        <v>5.9231</v>
       </c>
       <c r="X9" t="n">
-        <v>9.333299999999999</v>
+        <v>9.1538</v>
       </c>
       <c r="Y9" t="n">
-        <v>11.1667</v>
+        <v>10.9231</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03700763</v>
+        <v>0.03708711</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03305751</v>
+        <v>0.03314929</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>7.4342</v>
+        <v>7.5051</v>
       </c>
       <c r="AE9" t="n">
         <v>8</v>
@@ -1484,10 +1484,10 @@
         <v>10</v>
       </c>
       <c r="AH9" t="n">
-        <v>31329</v>
+        <v>31394</v>
       </c>
       <c r="AI9" t="n">
-        <v>6.9667</v>
+        <v>6.9859</v>
       </c>
     </row>
   </sheetData>

--- a/results/all_images/quantification/quantification_all_images.xlsx
+++ b/results/all_images/quantification/quantification_all_images.xlsx
@@ -620,7 +620,7 @@
         <v>3013</v>
       </c>
       <c r="G2" t="n">
-        <v>11.4</v>
+        <v>14.0667</v>
       </c>
       <c r="H2" t="n">
         <v>447.6667</v>
@@ -629,7 +629,7 @@
         <v>1016.0667</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03897445</v>
+        <v>0.03897941</v>
       </c>
       <c r="K2" t="n">
         <v>292.0698</v>
@@ -653,7 +653,7 @@
         <v>0.04050161</v>
       </c>
       <c r="R2" t="n">
-        <v>4.05</v>
+        <v>5.0246</v>
       </c>
       <c r="S2" t="n">
         <v>392.8667</v>
@@ -677,10 +677,10 @@
         <v>13.8667</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0441484</v>
+        <v>0.04415419</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.03892297</v>
+        <v>0.0389281</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>8.1572</v>
+        <v>8.1584</v>
       </c>
       <c r="AE2" t="n">
         <v>8.2462</v>
@@ -700,10 +700,10 @@
         <v>10.7703</v>
       </c>
       <c r="AH2" t="n">
-        <v>37978</v>
+        <v>37983</v>
       </c>
       <c r="AI2" t="n">
-        <v>7.5373</v>
+        <v>7.5443</v>
       </c>
     </row>
     <row r="3">
@@ -732,16 +732,16 @@
         <v>3684</v>
       </c>
       <c r="G3" t="n">
-        <v>6.1818</v>
+        <v>8.3636</v>
       </c>
       <c r="H3" t="n">
-        <v>399.2727</v>
+        <v>400.5455</v>
       </c>
       <c r="I3" t="n">
-        <v>1055.1818</v>
+        <v>1056.4545</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03641101</v>
+        <v>0.03642689</v>
       </c>
       <c r="K3" t="n">
         <v>349.6878</v>
@@ -759,25 +759,25 @@
         <v>0.9555</v>
       </c>
       <c r="P3" t="n">
-        <v>0.03273455</v>
+        <v>0.03283017</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03657206</v>
+        <v>0.03660992</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6497</v>
+        <v>2.3523</v>
       </c>
       <c r="S3" t="n">
-        <v>314.9091</v>
+        <v>319.5455</v>
       </c>
       <c r="T3" t="n">
-        <v>786</v>
+        <v>799.1818</v>
       </c>
       <c r="U3" t="n">
-        <v>444.7003</v>
+        <v>446.3275</v>
       </c>
       <c r="V3" t="n">
-        <v>1189.7529</v>
+        <v>1190.8061</v>
       </c>
       <c r="W3" t="n">
         <v>9.545500000000001</v>
@@ -789,10 +789,10 @@
         <v>15.8182</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.04114015</v>
+        <v>0.04115446</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.03634245</v>
+        <v>0.03635898</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>8.0998</v>
+        <v>8.1313</v>
       </c>
       <c r="AE3" t="n">
         <v>8.2462</v>
@@ -812,10 +812,10 @@
         <v>10.7703</v>
       </c>
       <c r="AH3" t="n">
-        <v>35180</v>
+        <v>35196</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.355</v>
+        <v>7.4383</v>
       </c>
     </row>
     <row r="4">
@@ -844,16 +844,16 @@
         <v>2066</v>
       </c>
       <c r="G4" t="n">
-        <v>3.5833</v>
+        <v>5.9167</v>
       </c>
       <c r="H4" t="n">
-        <v>272.1667</v>
+        <v>271.5833</v>
       </c>
       <c r="I4" t="n">
-        <v>859.1667</v>
+        <v>855.0833</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03689268</v>
+        <v>0.03680774</v>
       </c>
       <c r="K4" t="n">
         <v>222.1007</v>
@@ -871,40 +871,40 @@
         <v>0.9814000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0309508</v>
+        <v>0.0308937</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03889819</v>
+        <v>0.03874315</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5461</v>
+        <v>2.63</v>
       </c>
       <c r="S4" t="n">
-        <v>220</v>
+        <v>220.3333</v>
       </c>
       <c r="T4" t="n">
-        <v>642.75</v>
+        <v>638.6667</v>
       </c>
       <c r="U4" t="n">
-        <v>306.1293</v>
+        <v>305.5257</v>
       </c>
       <c r="V4" t="n">
-        <v>981.0484</v>
+        <v>976.5997</v>
       </c>
       <c r="W4" t="n">
-        <v>7.1667</v>
+        <v>7</v>
       </c>
       <c r="X4" t="n">
         <v>9.916700000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.3333</v>
+        <v>12.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.04200993</v>
+        <v>0.04191481</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03689268</v>
+        <v>0.03680774</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>7.8995</v>
+        <v>7.9055</v>
       </c>
       <c r="AE4" t="n">
         <v>8</v>
@@ -924,10 +924,10 @@
         <v>10.198</v>
       </c>
       <c r="AH4" t="n">
-        <v>37787</v>
+        <v>37700</v>
       </c>
       <c r="AI4" t="n">
-        <v>7.346</v>
+        <v>7.3971</v>
       </c>
     </row>
     <row r="5">
@@ -956,16 +956,16 @@
         <v>2188.5</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5</v>
+        <v>4.3333</v>
       </c>
       <c r="H5" t="n">
-        <v>242.3333</v>
+        <v>243.3333</v>
       </c>
       <c r="I5" t="n">
-        <v>762.25</v>
+        <v>765.9167</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03476352</v>
+        <v>0.0348182</v>
       </c>
       <c r="K5" t="n">
         <v>221.0149</v>
@@ -983,25 +983,25 @@
         <v>0.9801</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02560946</v>
+        <v>0.02571356</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03384685</v>
+        <v>0.03401309</v>
       </c>
       <c r="R5" t="n">
-        <v>0.8924</v>
+        <v>1.6316</v>
       </c>
       <c r="S5" t="n">
-        <v>187.5833</v>
+        <v>188</v>
       </c>
       <c r="T5" t="n">
-        <v>476.1667</v>
+        <v>495.75</v>
       </c>
       <c r="U5" t="n">
-        <v>273.5523</v>
+        <v>274.8571</v>
       </c>
       <c r="V5" t="n">
-        <v>867.2576</v>
+        <v>872.1635</v>
       </c>
       <c r="W5" t="n">
         <v>5.8333</v>
@@ -1013,10 +1013,10 @@
         <v>10.4167</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03959204</v>
+        <v>0.03965963</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.03476352</v>
+        <v>0.0348182</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>7.7041</v>
+        <v>7.7284</v>
       </c>
       <c r="AE5" t="n">
         <v>8</v>
@@ -1036,10 +1036,10 @@
         <v>10</v>
       </c>
       <c r="AH5" t="n">
-        <v>35600</v>
+        <v>35656</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.8669</v>
+        <v>6.9985</v>
       </c>
     </row>
     <row r="6">
@@ -1068,16 +1068,16 @@
         <v>1736</v>
       </c>
       <c r="G6" t="n">
-        <v>4.3636</v>
+        <v>6.3636</v>
       </c>
       <c r="H6" t="n">
-        <v>310.3636</v>
+        <v>311</v>
       </c>
       <c r="I6" t="n">
-        <v>922.8182</v>
+        <v>923.7273</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04023368</v>
+        <v>0.04024632</v>
       </c>
       <c r="K6" t="n">
         <v>207.4787</v>
@@ -1095,40 +1095,40 @@
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03743945</v>
+        <v>0.03751996</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.042466</v>
+        <v>0.04250902</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1027</v>
+        <v>3.113</v>
       </c>
       <c r="S6" t="n">
-        <v>244.9091</v>
+        <v>245.5455</v>
       </c>
       <c r="T6" t="n">
-        <v>657.9091</v>
+        <v>658.8182</v>
       </c>
       <c r="U6" t="n">
-        <v>352.2418</v>
+        <v>352.9911</v>
       </c>
       <c r="V6" t="n">
-        <v>1046.4873</v>
+        <v>1047.5094</v>
       </c>
       <c r="W6" t="n">
         <v>6.8182</v>
       </c>
       <c r="X6" t="n">
-        <v>11</v>
+        <v>11.0909</v>
       </c>
       <c r="Y6" t="n">
         <v>13.4545</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.04570415</v>
+        <v>0.045718</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.04023368</v>
+        <v>0.04024632</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>7.6176</v>
+        <v>7.6274</v>
       </c>
       <c r="AE6" t="n">
         <v>8</v>
@@ -1148,10 +1148,10 @@
         <v>10</v>
       </c>
       <c r="AH6" t="n">
-        <v>41364</v>
+        <v>41377</v>
       </c>
       <c r="AI6" t="n">
-        <v>7.0667</v>
+        <v>7.1679</v>
       </c>
     </row>
     <row r="7">
@@ -1180,16 +1180,16 @@
         <v>2671.5</v>
       </c>
       <c r="G7" t="n">
-        <v>8.333299999999999</v>
+        <v>10.6667</v>
       </c>
       <c r="H7" t="n">
-        <v>415</v>
+        <v>415.1111</v>
       </c>
       <c r="I7" t="n">
-        <v>979.3333</v>
+        <v>979.4444</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03447141</v>
+        <v>0.03447239</v>
       </c>
       <c r="K7" t="n">
         <v>253.4606</v>
@@ -1207,25 +1207,25 @@
         <v>0.9809</v>
       </c>
       <c r="P7" t="n">
-        <v>0.04040066</v>
+        <v>0.04041286</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.04036312</v>
+        <v>0.04036778</v>
       </c>
       <c r="R7" t="n">
-        <v>3.4633</v>
+        <v>4.5208</v>
       </c>
       <c r="S7" t="n">
-        <v>359.1111</v>
+        <v>359.2222</v>
       </c>
       <c r="T7" t="n">
-        <v>808.1111</v>
+        <v>808.2222</v>
       </c>
       <c r="U7" t="n">
-        <v>469.7742</v>
+        <v>469.9774</v>
       </c>
       <c r="V7" t="n">
-        <v>1107.8014</v>
+        <v>1108.0045</v>
       </c>
       <c r="W7" t="n">
         <v>9.777799999999999</v>
@@ -1237,10 +1237,10 @@
         <v>14.5556</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03880816</v>
+        <v>0.03880996</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.03544909</v>
+        <v>0.03545015</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>7.5333</v>
+        <v>7.5343</v>
       </c>
       <c r="AE7" t="n">
         <v>8</v>
@@ -1260,10 +1260,10 @@
         <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>33418</v>
+        <v>33419</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.9508</v>
+        <v>6.9608</v>
       </c>
     </row>
     <row r="8">
@@ -1292,16 +1292,16 @@
         <v>1519</v>
       </c>
       <c r="G8" t="n">
-        <v>5.9091</v>
+        <v>7.4545</v>
       </c>
       <c r="H8" t="n">
-        <v>315.1818</v>
+        <v>315.8182</v>
       </c>
       <c r="I8" t="n">
-        <v>864.1818</v>
+        <v>865.0909</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03524355</v>
+        <v>0.03525724</v>
       </c>
       <c r="K8" t="n">
         <v>221.5717</v>
@@ -1319,25 +1319,25 @@
         <v>0.9972</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03580719</v>
+        <v>0.03588123</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03881081</v>
+        <v>0.03885196</v>
       </c>
       <c r="R8" t="n">
-        <v>2.7497</v>
+        <v>3.4794</v>
       </c>
       <c r="S8" t="n">
-        <v>256.9091</v>
+        <v>257.5455</v>
       </c>
       <c r="T8" t="n">
-        <v>596.4545000000001</v>
+        <v>597.3636</v>
       </c>
       <c r="U8" t="n">
-        <v>356.2859</v>
+        <v>356.9975</v>
       </c>
       <c r="V8" t="n">
-        <v>975.7318</v>
+        <v>976.7915</v>
       </c>
       <c r="W8" t="n">
         <v>7.5455</v>
@@ -1349,10 +1349,10 @@
         <v>12.7273</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03988112</v>
+        <v>0.03989781</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03614952</v>
+        <v>0.03616411</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -1360,7 +1360,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>7.7083</v>
+        <v>7.7188</v>
       </c>
       <c r="AE8" t="n">
         <v>8</v>
@@ -1372,10 +1372,10 @@
         <v>10.198</v>
       </c>
       <c r="AH8" t="n">
-        <v>34694</v>
+        <v>34708</v>
       </c>
       <c r="AI8" t="n">
-        <v>7.1227</v>
+        <v>7.1595</v>
       </c>
     </row>
     <row r="9">
@@ -1404,16 +1404,16 @@
         <v>1511.5</v>
       </c>
       <c r="G9" t="n">
-        <v>5.4615</v>
+        <v>6.1538</v>
       </c>
       <c r="H9" t="n">
-        <v>263.9231</v>
+        <v>264.5385</v>
       </c>
       <c r="I9" t="n">
-        <v>707</v>
+        <v>708.9231</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03282691</v>
+        <v>0.03286895</v>
       </c>
       <c r="K9" t="n">
         <v>186.0541</v>
@@ -1431,25 +1431,25 @@
         <v>0.9839</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03487364</v>
+        <v>0.0349763</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03693351</v>
+        <v>0.03703612</v>
       </c>
       <c r="R9" t="n">
-        <v>2.9942</v>
+        <v>3.3705</v>
       </c>
       <c r="S9" t="n">
-        <v>198.8462</v>
+        <v>200.0769</v>
       </c>
       <c r="T9" t="n">
-        <v>463</v>
+        <v>464.6154</v>
       </c>
       <c r="U9" t="n">
-        <v>294.7215</v>
+        <v>295.3183</v>
       </c>
       <c r="V9" t="n">
-        <v>793.1523999999999</v>
+        <v>795.5107</v>
       </c>
       <c r="W9" t="n">
         <v>5.9231</v>
@@ -1461,10 +1461,10 @@
         <v>10.9231</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03708711</v>
+        <v>0.03713687</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03314929</v>
+        <v>0.03319469</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>7.5051</v>
+        <v>7.516</v>
       </c>
       <c r="AE9" t="n">
         <v>8</v>
@@ -1484,10 +1484,10 @@
         <v>10</v>
       </c>
       <c r="AH9" t="n">
-        <v>31394</v>
+        <v>31437</v>
       </c>
       <c r="AI9" t="n">
-        <v>6.9859</v>
+        <v>7.0539</v>
       </c>
     </row>
   </sheetData>

--- a/results/all_images/quantification/quantification_all_images.xlsx
+++ b/results/all_images/quantification/quantification_all_images.xlsx
@@ -620,16 +620,16 @@
         <v>3013</v>
       </c>
       <c r="G2" t="n">
-        <v>14.0667</v>
+        <v>14.5333</v>
       </c>
       <c r="H2" t="n">
-        <v>447.6667</v>
+        <v>473.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1016.0667</v>
+        <v>1032.7333</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03897941</v>
+        <v>0.03963621</v>
       </c>
       <c r="K2" t="n">
         <v>292.0698</v>
@@ -647,40 +647,40 @@
         <v>0.9858</v>
       </c>
       <c r="P2" t="n">
-        <v>0.04176754</v>
+        <v>0.04403868</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.04050161</v>
+        <v>0.04109938</v>
       </c>
       <c r="R2" t="n">
-        <v>5.0246</v>
+        <v>5.1783</v>
       </c>
       <c r="S2" t="n">
-        <v>392.8667</v>
+        <v>424.8667</v>
       </c>
       <c r="T2" t="n">
-        <v>810.2</v>
+        <v>852.9333</v>
       </c>
       <c r="U2" t="n">
-        <v>509.1242</v>
+        <v>538.1704</v>
       </c>
       <c r="V2" t="n">
-        <v>1153.1702</v>
+        <v>1172.3557</v>
       </c>
       <c r="W2" t="n">
-        <v>9.6</v>
+        <v>10.7333</v>
       </c>
       <c r="X2" t="n">
-        <v>13.2667</v>
+        <v>13.1333</v>
       </c>
       <c r="Y2" t="n">
-        <v>13.8667</v>
+        <v>13.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.04415419</v>
+        <v>0.0448956</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0389281</v>
+        <v>0.03960452</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>8.1584</v>
+        <v>8.1721</v>
       </c>
       <c r="AE2" t="n">
         <v>8.2462</v>
@@ -700,10 +700,10 @@
         <v>10.7703</v>
       </c>
       <c r="AH2" t="n">
-        <v>37983</v>
+        <v>38643</v>
       </c>
       <c r="AI2" t="n">
-        <v>7.5443</v>
+        <v>7.4697</v>
       </c>
     </row>
     <row r="3">
@@ -732,16 +732,16 @@
         <v>3684</v>
       </c>
       <c r="G3" t="n">
-        <v>8.3636</v>
+        <v>10.3636</v>
       </c>
       <c r="H3" t="n">
-        <v>400.5455</v>
+        <v>452.7273</v>
       </c>
       <c r="I3" t="n">
-        <v>1056.4545</v>
+        <v>1131.8182</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03642689</v>
+        <v>0.03797976</v>
       </c>
       <c r="K3" t="n">
         <v>349.6878</v>
@@ -759,40 +759,40 @@
         <v>0.9555</v>
       </c>
       <c r="P3" t="n">
-        <v>0.03283017</v>
+        <v>0.0370072</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03660992</v>
+        <v>0.03902158</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3523</v>
+        <v>2.9114</v>
       </c>
       <c r="S3" t="n">
-        <v>319.5455</v>
+        <v>388.6364</v>
       </c>
       <c r="T3" t="n">
-        <v>799.1818</v>
+        <v>924.4545000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>446.3275</v>
+        <v>507.2729</v>
       </c>
       <c r="V3" t="n">
-        <v>1190.8061</v>
+        <v>1278.6951</v>
       </c>
       <c r="W3" t="n">
-        <v>9.545500000000001</v>
+        <v>11.1818</v>
       </c>
       <c r="X3" t="n">
-        <v>14.1818</v>
+        <v>15.0909</v>
       </c>
       <c r="Y3" t="n">
-        <v>15.8182</v>
+        <v>16.1818</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.04115446</v>
+        <v>0.04293196</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.03635898</v>
+        <v>0.03794367</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>8.1313</v>
+        <v>8.220700000000001</v>
       </c>
       <c r="AE3" t="n">
         <v>8.2462</v>
@@ -812,10 +812,10 @@
         <v>10.7703</v>
       </c>
       <c r="AH3" t="n">
-        <v>35196</v>
+        <v>36730</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.4383</v>
+        <v>7.5225</v>
       </c>
     </row>
     <row r="4">
@@ -844,16 +844,16 @@
         <v>2066</v>
       </c>
       <c r="G4" t="n">
-        <v>5.9167</v>
+        <v>7.6667</v>
       </c>
       <c r="H4" t="n">
-        <v>271.5833</v>
+        <v>340.4167</v>
       </c>
       <c r="I4" t="n">
-        <v>855.0833</v>
+        <v>984.4167</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03680774</v>
+        <v>0.03941846</v>
       </c>
       <c r="K4" t="n">
         <v>222.1007</v>
@@ -871,40 +871,40 @@
         <v>0.9814000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0308937</v>
+        <v>0.0386731</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03874315</v>
+        <v>0.04434147</v>
       </c>
       <c r="R4" t="n">
-        <v>2.63</v>
+        <v>3.3796</v>
       </c>
       <c r="S4" t="n">
-        <v>220.3333</v>
+        <v>287.5833</v>
       </c>
       <c r="T4" t="n">
-        <v>638.6667</v>
+        <v>794.5</v>
       </c>
       <c r="U4" t="n">
-        <v>305.5257</v>
+        <v>384.5349</v>
       </c>
       <c r="V4" t="n">
-        <v>976.5997</v>
+        <v>1125.117</v>
       </c>
       <c r="W4" t="n">
-        <v>7</v>
+        <v>8.833299999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>9.916700000000001</v>
+        <v>11.8333</v>
       </c>
       <c r="Y4" t="n">
-        <v>12.25</v>
+        <v>13.9167</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.04191481</v>
+        <v>0.04490581</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03680774</v>
+        <v>0.03941846</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
@@ -912,22 +912,22 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>7.9055</v>
+        <v>8.0052</v>
       </c>
       <c r="AE4" t="n">
         <v>8</v>
       </c>
       <c r="AF4" t="n">
-        <v>4.4721</v>
+        <v>5.6569</v>
       </c>
       <c r="AG4" t="n">
         <v>10.198</v>
       </c>
       <c r="AH4" t="n">
-        <v>37700</v>
+        <v>40374</v>
       </c>
       <c r="AI4" t="n">
-        <v>7.3971</v>
+        <v>7.5002</v>
       </c>
     </row>
     <row r="5">
@@ -956,16 +956,16 @@
         <v>2188.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4.3333</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
-        <v>243.3333</v>
+        <v>290.75</v>
       </c>
       <c r="I5" t="n">
-        <v>765.9167</v>
+        <v>879.8333</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0348182</v>
+        <v>0.03716181</v>
       </c>
       <c r="K5" t="n">
         <v>221.0149</v>
@@ -983,40 +983,40 @@
         <v>0.9801</v>
       </c>
       <c r="P5" t="n">
-        <v>0.02571356</v>
+        <v>0.0319145</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03401309</v>
+        <v>0.04000397</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6316</v>
+        <v>2.7051</v>
       </c>
       <c r="S5" t="n">
-        <v>188</v>
+        <v>245.75</v>
       </c>
       <c r="T5" t="n">
-        <v>495.75</v>
+        <v>656.75</v>
       </c>
       <c r="U5" t="n">
-        <v>274.8571</v>
+        <v>329.306</v>
       </c>
       <c r="V5" t="n">
-        <v>872.1635</v>
+        <v>1003.1156</v>
       </c>
       <c r="W5" t="n">
-        <v>5.8333</v>
+        <v>7.4167</v>
       </c>
       <c r="X5" t="n">
-        <v>9.333299999999999</v>
+        <v>10.0833</v>
       </c>
       <c r="Y5" t="n">
-        <v>10.4167</v>
+        <v>11.9167</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.03965963</v>
+        <v>0.0423432</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0348182</v>
+        <v>0.03716181</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>7.7284</v>
+        <v>7.8159</v>
       </c>
       <c r="AE5" t="n">
         <v>8</v>
@@ -1033,13 +1033,13 @@
         <v>4.4721</v>
       </c>
       <c r="AG5" t="n">
-        <v>10</v>
+        <v>10.198</v>
       </c>
       <c r="AH5" t="n">
-        <v>35656</v>
+        <v>38056</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.9985</v>
+        <v>7.1739</v>
       </c>
     </row>
     <row r="6">
@@ -1068,16 +1068,16 @@
         <v>1736</v>
       </c>
       <c r="G6" t="n">
-        <v>6.3636</v>
+        <v>7.4545</v>
       </c>
       <c r="H6" t="n">
-        <v>311</v>
+        <v>351.1818</v>
       </c>
       <c r="I6" t="n">
-        <v>923.7273</v>
+        <v>971.6364</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04024632</v>
+        <v>0.04199519</v>
       </c>
       <c r="K6" t="n">
         <v>207.4787</v>
@@ -1095,40 +1095,40 @@
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>0.03751996</v>
+        <v>0.04236469</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.04250902</v>
+        <v>0.04466928</v>
       </c>
       <c r="R6" t="n">
-        <v>3.113</v>
+        <v>3.6357</v>
       </c>
       <c r="S6" t="n">
-        <v>245.5455</v>
+        <v>308.4545</v>
       </c>
       <c r="T6" t="n">
-        <v>658.8182</v>
+        <v>771.1818</v>
       </c>
       <c r="U6" t="n">
-        <v>352.9911</v>
+        <v>398.4307</v>
       </c>
       <c r="V6" t="n">
-        <v>1047.5094</v>
+        <v>1099.8699</v>
       </c>
       <c r="W6" t="n">
-        <v>6.8182</v>
+        <v>8.545500000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>11.0909</v>
+        <v>11.7273</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.4545</v>
+        <v>13.3636</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.045718</v>
+        <v>0.04769718</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.04024632</v>
+        <v>0.04199519</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>7.6274</v>
+        <v>7.7697</v>
       </c>
       <c r="AE6" t="n">
         <v>8</v>
@@ -1148,10 +1148,10 @@
         <v>10</v>
       </c>
       <c r="AH6" t="n">
-        <v>41377</v>
+        <v>43175</v>
       </c>
       <c r="AI6" t="n">
-        <v>7.1679</v>
+        <v>7.3107</v>
       </c>
     </row>
     <row r="7">
@@ -1180,16 +1180,16 @@
         <v>2671.5</v>
       </c>
       <c r="G7" t="n">
-        <v>10.6667</v>
+        <v>12.5556</v>
       </c>
       <c r="H7" t="n">
-        <v>415.1111</v>
+        <v>454.1111</v>
       </c>
       <c r="I7" t="n">
-        <v>979.4444</v>
+        <v>1028.1111</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03447239</v>
+        <v>0.03597973</v>
       </c>
       <c r="K7" t="n">
         <v>253.4606</v>
@@ -1207,40 +1207,40 @@
         <v>0.9809</v>
       </c>
       <c r="P7" t="n">
-        <v>0.04041286</v>
+        <v>0.04403147</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.04036778</v>
+        <v>0.04241266</v>
       </c>
       <c r="R7" t="n">
-        <v>4.5208</v>
+        <v>5.0992</v>
       </c>
       <c r="S7" t="n">
-        <v>359.2222</v>
+        <v>408.1111</v>
       </c>
       <c r="T7" t="n">
-        <v>808.2222</v>
+        <v>873.5556</v>
       </c>
       <c r="U7" t="n">
-        <v>469.9774</v>
+        <v>513.9893</v>
       </c>
       <c r="V7" t="n">
-        <v>1108.0045</v>
+        <v>1162.9909</v>
       </c>
       <c r="W7" t="n">
-        <v>9.777799999999999</v>
+        <v>10.6667</v>
       </c>
       <c r="X7" t="n">
-        <v>13</v>
+        <v>13.2222</v>
       </c>
       <c r="Y7" t="n">
-        <v>14.5556</v>
+        <v>14.8889</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.03880996</v>
+        <v>0.04048176</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.03545015</v>
+        <v>0.0370742</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>7.5343</v>
+        <v>7.5197</v>
       </c>
       <c r="AE7" t="n">
         <v>8</v>
@@ -1260,10 +1260,10 @@
         <v>10</v>
       </c>
       <c r="AH7" t="n">
-        <v>33419</v>
+        <v>34950</v>
       </c>
       <c r="AI7" t="n">
-        <v>6.9608</v>
+        <v>6.8931</v>
       </c>
     </row>
     <row r="8">
@@ -1292,16 +1292,16 @@
         <v>1519</v>
       </c>
       <c r="G8" t="n">
-        <v>7.4545</v>
+        <v>8.6364</v>
       </c>
       <c r="H8" t="n">
-        <v>315.8182</v>
+        <v>348.3636</v>
       </c>
       <c r="I8" t="n">
-        <v>865.0909</v>
+        <v>900.9091</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03525724</v>
+        <v>0.03751105</v>
       </c>
       <c r="K8" t="n">
         <v>221.5717</v>
@@ -1319,40 +1319,40 @@
         <v>0.9972</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03588123</v>
+        <v>0.03965443</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03885196</v>
+        <v>0.0404533</v>
       </c>
       <c r="R8" t="n">
-        <v>3.4794</v>
+        <v>4.0142</v>
       </c>
       <c r="S8" t="n">
-        <v>257.5455</v>
+        <v>302.2727</v>
       </c>
       <c r="T8" t="n">
-        <v>597.3636</v>
+        <v>674.4545000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>356.9975</v>
+        <v>393.8255</v>
       </c>
       <c r="V8" t="n">
-        <v>976.7915</v>
+        <v>1017.4285</v>
       </c>
       <c r="W8" t="n">
-        <v>7.5455</v>
+        <v>8.3636</v>
       </c>
       <c r="X8" t="n">
-        <v>10.7273</v>
+        <v>11.0909</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.7273</v>
+        <v>12.8182</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.03989781</v>
+        <v>0.0424887</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03616411</v>
+        <v>0.03854185</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
@@ -1360,22 +1360,22 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>7.7188</v>
+        <v>7.7464</v>
       </c>
       <c r="AE8" t="n">
         <v>8</v>
       </c>
       <c r="AF8" t="n">
-        <v>4</v>
+        <v>4.4721</v>
       </c>
       <c r="AG8" t="n">
         <v>10.198</v>
       </c>
       <c r="AH8" t="n">
-        <v>34708</v>
+        <v>36990</v>
       </c>
       <c r="AI8" t="n">
-        <v>7.1595</v>
+        <v>7.1663</v>
       </c>
     </row>
     <row r="9">
@@ -1404,16 +1404,16 @@
         <v>1511.5</v>
       </c>
       <c r="G9" t="n">
-        <v>6.1538</v>
+        <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>264.5385</v>
+        <v>299.6154</v>
       </c>
       <c r="I9" t="n">
-        <v>708.9231</v>
+        <v>749.4615</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03286895</v>
+        <v>0.03603597</v>
       </c>
       <c r="K9" t="n">
         <v>186.0541</v>
@@ -1431,40 +1431,40 @@
         <v>0.9839</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0349763</v>
+        <v>0.03944967</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03703612</v>
+        <v>0.03909379</v>
       </c>
       <c r="R9" t="n">
-        <v>3.3705</v>
+        <v>3.8347</v>
       </c>
       <c r="S9" t="n">
-        <v>200.0769</v>
+        <v>257.3846</v>
       </c>
       <c r="T9" t="n">
-        <v>464.6154</v>
+        <v>560.7692</v>
       </c>
       <c r="U9" t="n">
-        <v>295.3183</v>
+        <v>335.9725</v>
       </c>
       <c r="V9" t="n">
-        <v>795.5107</v>
+        <v>842.489</v>
       </c>
       <c r="W9" t="n">
-        <v>5.9231</v>
+        <v>7.1538</v>
       </c>
       <c r="X9" t="n">
-        <v>9.1538</v>
+        <v>9.8462</v>
       </c>
       <c r="Y9" t="n">
-        <v>10.9231</v>
+        <v>11</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.03713687</v>
+        <v>0.04073355</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03319469</v>
+        <v>0.03647435</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>7.516</v>
+        <v>7.6752</v>
       </c>
       <c r="AE9" t="n">
         <v>8</v>
@@ -1481,13 +1481,13 @@
         <v>4</v>
       </c>
       <c r="AG9" t="n">
-        <v>10</v>
+        <v>10.198</v>
       </c>
       <c r="AH9" t="n">
-        <v>31437</v>
+        <v>34543</v>
       </c>
       <c r="AI9" t="n">
-        <v>7.0539</v>
+        <v>7.0396</v>
       </c>
     </row>
   </sheetData>

--- a/results/all_images/quantification/quantification_all_images.xlsx
+++ b/results/all_images/quantification/quantification_all_images.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI9"/>
+  <dimension ref="A1:AM9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,35 +560,55 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>loops per cell</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>share of a cell's edges on a loop</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>loops per field</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>share of field edges on a loop</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>image_label</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>canalicular width mean (px)</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>canalicular width median (px)</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>canalicular width p10 (px)</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>canalicular width p90 (px)</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>canalicular width pixels used</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>canalicular width in ring 30 px per cell (px)</t>
         </is>
@@ -620,16 +640,16 @@
         <v>3013</v>
       </c>
       <c r="G2" t="n">
-        <v>14.5333</v>
+        <v>15.1333</v>
       </c>
       <c r="H2" t="n">
-        <v>473.2</v>
+        <v>485.5333</v>
       </c>
       <c r="I2" t="n">
-        <v>1032.7333</v>
+        <v>1045.7333</v>
       </c>
       <c r="J2" t="n">
-        <v>0.03963621</v>
+        <v>0.03994225</v>
       </c>
       <c r="K2" t="n">
         <v>292.0698</v>
@@ -647,63 +667,75 @@
         <v>0.9858</v>
       </c>
       <c r="P2" t="n">
-        <v>0.04403868</v>
+        <v>0.04568601</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.04109938</v>
+        <v>0.04182451</v>
       </c>
       <c r="R2" t="n">
-        <v>5.1783</v>
+        <v>5.546</v>
       </c>
       <c r="S2" t="n">
-        <v>424.8667</v>
+        <v>445.2667</v>
       </c>
       <c r="T2" t="n">
-        <v>852.9333</v>
+        <v>892.7333</v>
       </c>
       <c r="U2" t="n">
-        <v>538.1704</v>
+        <v>552.5835</v>
       </c>
       <c r="V2" t="n">
-        <v>1172.3557</v>
+        <v>1187.5687</v>
       </c>
       <c r="W2" t="n">
         <v>10.7333</v>
       </c>
       <c r="X2" t="n">
-        <v>13.1333</v>
+        <v>13.2667</v>
       </c>
       <c r="Y2" t="n">
-        <v>13.6</v>
+        <v>13.6667</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.0448956</v>
+        <v>0.04524032</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.03960452</v>
-      </c>
-      <c r="AC2" t="inlineStr">
+        <v>0.03982589</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.2613</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>159</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>542_z06</t>
         </is>
       </c>
-      <c r="AD2" t="n">
-        <v>8.1721</v>
-      </c>
-      <c r="AE2" t="n">
+      <c r="AH2" t="n">
+        <v>8.2188</v>
+      </c>
+      <c r="AI2" t="n">
         <v>8.2462</v>
       </c>
-      <c r="AF2" t="n">
-        <v>4.4721</v>
-      </c>
-      <c r="AG2" t="n">
+      <c r="AJ2" t="n">
+        <v>5.6569</v>
+      </c>
+      <c r="AK2" t="n">
         <v>10.7703</v>
       </c>
-      <c r="AH2" t="n">
-        <v>38643</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>7.4697</v>
+      <c r="AL2" t="n">
+        <v>38859</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>7.6454</v>
       </c>
     </row>
     <row r="3">
@@ -732,16 +764,16 @@
         <v>3684</v>
       </c>
       <c r="G3" t="n">
-        <v>10.3636</v>
+        <v>11.8182</v>
       </c>
       <c r="H3" t="n">
-        <v>452.7273</v>
+        <v>478.0909</v>
       </c>
       <c r="I3" t="n">
-        <v>1131.8182</v>
+        <v>1163.5455</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03797976</v>
+        <v>0.03890414</v>
       </c>
       <c r="K3" t="n">
         <v>349.6878</v>
@@ -759,63 +791,75 @@
         <v>0.9555</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0370072</v>
+        <v>0.03936536</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03902158</v>
+        <v>0.04019659</v>
       </c>
       <c r="R3" t="n">
-        <v>2.9114</v>
+        <v>3.316</v>
       </c>
       <c r="S3" t="n">
-        <v>388.6364</v>
+        <v>429.6364</v>
       </c>
       <c r="T3" t="n">
-        <v>924.4545000000001</v>
+        <v>987.3636</v>
       </c>
       <c r="U3" t="n">
-        <v>507.2729</v>
+        <v>536.5021</v>
       </c>
       <c r="V3" t="n">
-        <v>1278.6951</v>
+        <v>1315.11</v>
       </c>
       <c r="W3" t="n">
-        <v>11.1818</v>
+        <v>11.9091</v>
       </c>
       <c r="X3" t="n">
-        <v>15.0909</v>
+        <v>15.2727</v>
       </c>
       <c r="Y3" t="n">
-        <v>16.1818</v>
+        <v>16.4545</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.04293196</v>
+        <v>0.04398086</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.03794367</v>
-      </c>
-      <c r="AC3" t="inlineStr">
+        <v>0.03883208</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>10.8182</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>156</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>542_z18</t>
         </is>
       </c>
-      <c r="AD3" t="n">
-        <v>8.220700000000001</v>
-      </c>
-      <c r="AE3" t="n">
+      <c r="AH3" t="n">
+        <v>8.241099999999999</v>
+      </c>
+      <c r="AI3" t="n">
         <v>8.2462</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AJ3" t="n">
         <v>4.4721</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AK3" t="n">
         <v>10.7703</v>
       </c>
-      <c r="AH3" t="n">
-        <v>36730</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>7.5225</v>
+      <c r="AL3" t="n">
+        <v>37590</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>7.6437</v>
       </c>
     </row>
     <row r="4">
@@ -844,16 +888,16 @@
         <v>2066</v>
       </c>
       <c r="G4" t="n">
-        <v>7.6667</v>
+        <v>8.5</v>
       </c>
       <c r="H4" t="n">
-        <v>340.4167</v>
+        <v>369.5833</v>
       </c>
       <c r="I4" t="n">
-        <v>984.4167</v>
+        <v>1061.5833</v>
       </c>
       <c r="J4" t="n">
-        <v>0.03941846</v>
+        <v>0.04306115</v>
       </c>
       <c r="K4" t="n">
         <v>222.1007</v>
@@ -871,63 +915,75 @@
         <v>0.9814000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0386731</v>
+        <v>0.04190314</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.04434147</v>
+        <v>0.04754696</v>
       </c>
       <c r="R4" t="n">
-        <v>3.3796</v>
+        <v>3.7455</v>
       </c>
       <c r="S4" t="n">
-        <v>287.5833</v>
+        <v>326.75</v>
       </c>
       <c r="T4" t="n">
-        <v>794.5</v>
+        <v>931.0833</v>
       </c>
       <c r="U4" t="n">
-        <v>384.5349</v>
+        <v>417.2165</v>
       </c>
       <c r="V4" t="n">
-        <v>1125.117</v>
+        <v>1213.0975</v>
       </c>
       <c r="W4" t="n">
-        <v>8.833299999999999</v>
+        <v>9.75</v>
       </c>
       <c r="X4" t="n">
-        <v>11.8333</v>
+        <v>12.8333</v>
       </c>
       <c r="Y4" t="n">
-        <v>13.9167</v>
+        <v>14.3333</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.04490581</v>
+        <v>0.04903999</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.03941846</v>
-      </c>
-      <c r="AC4" t="inlineStr">
+        <v>0.04306115</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>19.0833</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>275</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.4908</v>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>543-2</t>
         </is>
       </c>
-      <c r="AD4" t="n">
-        <v>8.0052</v>
-      </c>
-      <c r="AE4" t="n">
+      <c r="AH4" t="n">
+        <v>8.023999999999999</v>
+      </c>
+      <c r="AI4" t="n">
         <v>8</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AJ4" t="n">
         <v>5.6569</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AK4" t="n">
         <v>10.198</v>
       </c>
-      <c r="AH4" t="n">
-        <v>40374</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>7.5002</v>
+      <c r="AL4" t="n">
+        <v>44105</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>7.701</v>
       </c>
     </row>
     <row r="5">
@@ -956,16 +1012,16 @@
         <v>2188.5</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
-        <v>290.75</v>
+        <v>325.5833</v>
       </c>
       <c r="I5" t="n">
-        <v>879.8333</v>
+        <v>941.5</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03716181</v>
+        <v>0.04029932</v>
       </c>
       <c r="K5" t="n">
         <v>221.0149</v>
@@ -983,63 +1039,75 @@
         <v>0.9801</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0319145</v>
+        <v>0.03667744</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.04000397</v>
+        <v>0.04310532</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7051</v>
+        <v>3.1711</v>
       </c>
       <c r="S5" t="n">
-        <v>245.75</v>
+        <v>288.6667</v>
       </c>
       <c r="T5" t="n">
-        <v>656.75</v>
+        <v>752.25</v>
       </c>
       <c r="U5" t="n">
-        <v>329.306</v>
+        <v>369.1527</v>
       </c>
       <c r="V5" t="n">
-        <v>1003.1156</v>
+        <v>1072.9679</v>
       </c>
       <c r="W5" t="n">
-        <v>7.4167</v>
+        <v>8.833299999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>10.0833</v>
+        <v>11.0833</v>
       </c>
       <c r="Y5" t="n">
-        <v>11.9167</v>
+        <v>13.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0423432</v>
+        <v>0.04591962</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.03716181</v>
-      </c>
-      <c r="AC5" t="inlineStr">
+        <v>0.04029932</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>17.3333</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>244</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.4439</v>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>543_3</t>
         </is>
       </c>
-      <c r="AD5" t="n">
-        <v>7.8159</v>
-      </c>
-      <c r="AE5" t="n">
+      <c r="AH5" t="n">
+        <v>7.9145</v>
+      </c>
+      <c r="AI5" t="n">
         <v>8</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AJ5" t="n">
         <v>4.4721</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AK5" t="n">
         <v>10.198</v>
       </c>
-      <c r="AH5" t="n">
-        <v>38056</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>7.1739</v>
+      <c r="AL5" t="n">
+        <v>41269</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>7.4443</v>
       </c>
     </row>
     <row r="6">
@@ -1068,16 +1136,16 @@
         <v>1736</v>
       </c>
       <c r="G6" t="n">
-        <v>7.4545</v>
+        <v>9.2727</v>
       </c>
       <c r="H6" t="n">
-        <v>351.1818</v>
+        <v>377.1818</v>
       </c>
       <c r="I6" t="n">
-        <v>971.6364</v>
+        <v>1028.1818</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04199519</v>
+        <v>0.04303692</v>
       </c>
       <c r="K6" t="n">
         <v>207.4787</v>
@@ -1095,63 +1163,75 @@
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>0.04236469</v>
+        <v>0.04528973</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.04466928</v>
+        <v>0.04719016</v>
       </c>
       <c r="R6" t="n">
-        <v>3.6357</v>
+        <v>4.4972</v>
       </c>
       <c r="S6" t="n">
-        <v>308.4545</v>
+        <v>337.5455</v>
       </c>
       <c r="T6" t="n">
-        <v>771.1818</v>
+        <v>825.8182</v>
       </c>
       <c r="U6" t="n">
-        <v>398.4307</v>
+        <v>427.512</v>
       </c>
       <c r="V6" t="n">
-        <v>1099.8699</v>
+        <v>1164.1805</v>
       </c>
       <c r="W6" t="n">
-        <v>8.545500000000001</v>
+        <v>9</v>
       </c>
       <c r="X6" t="n">
-        <v>11.7273</v>
+        <v>12.6364</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.3636</v>
+        <v>13.8182</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.04769718</v>
+        <v>0.04889348</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.04199519</v>
-      </c>
-      <c r="AC6" t="inlineStr">
+        <v>0.04303692</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>17.1818</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.4033</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>231</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>543_z13</t>
         </is>
       </c>
-      <c r="AD6" t="n">
-        <v>7.7697</v>
-      </c>
-      <c r="AE6" t="n">
+      <c r="AH6" t="n">
+        <v>7.7853</v>
+      </c>
+      <c r="AI6" t="n">
         <v>8</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AJ6" t="n">
         <v>4.4721</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AK6" t="n">
         <v>10</v>
       </c>
-      <c r="AH6" t="n">
-        <v>43175</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>7.3107</v>
+      <c r="AL6" t="n">
+        <v>44246</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>7.3801</v>
       </c>
     </row>
     <row r="7">
@@ -1180,16 +1260,16 @@
         <v>2671.5</v>
       </c>
       <c r="G7" t="n">
-        <v>12.5556</v>
+        <v>12.3333</v>
       </c>
       <c r="H7" t="n">
-        <v>454.1111</v>
+        <v>463.1111</v>
       </c>
       <c r="I7" t="n">
-        <v>1028.1111</v>
+        <v>1040.4444</v>
       </c>
       <c r="J7" t="n">
-        <v>0.03597973</v>
+        <v>0.03635411</v>
       </c>
       <c r="K7" t="n">
         <v>253.4606</v>
@@ -1207,63 +1287,75 @@
         <v>0.9809</v>
       </c>
       <c r="P7" t="n">
-        <v>0.04403147</v>
+        <v>0.04539679</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.04241266</v>
+        <v>0.0431795</v>
       </c>
       <c r="R7" t="n">
-        <v>5.0992</v>
+        <v>5.1608</v>
       </c>
       <c r="S7" t="n">
-        <v>408.1111</v>
+        <v>423.8889</v>
       </c>
       <c r="T7" t="n">
-        <v>873.5556</v>
+        <v>899.4444</v>
       </c>
       <c r="U7" t="n">
-        <v>513.9893</v>
+        <v>524.8605</v>
       </c>
       <c r="V7" t="n">
-        <v>1162.9909</v>
+        <v>1178.3413</v>
       </c>
       <c r="W7" t="n">
-        <v>10.6667</v>
+        <v>11.1111</v>
       </c>
       <c r="X7" t="n">
-        <v>13.2222</v>
+        <v>13.5556</v>
       </c>
       <c r="Y7" t="n">
-        <v>14.8889</v>
+        <v>15</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.04048176</v>
+        <v>0.04091913</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.0370742</v>
-      </c>
-      <c r="AC7" t="inlineStr">
+        <v>0.03741577</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>14.2222</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>181</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="AG7" t="inlineStr">
         <is>
           <t>682_z08</t>
         </is>
       </c>
-      <c r="AD7" t="n">
-        <v>7.5197</v>
-      </c>
-      <c r="AE7" t="n">
+      <c r="AH7" t="n">
+        <v>7.5429</v>
+      </c>
+      <c r="AI7" t="n">
         <v>8</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AJ7" t="n">
         <v>4</v>
       </c>
-      <c r="AG7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>34950</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>6.8931</v>
+      <c r="AK7" t="n">
+        <v>10.1782</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>35272</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>7.1358</v>
       </c>
     </row>
     <row r="8">
@@ -1292,16 +1384,16 @@
         <v>1519</v>
       </c>
       <c r="G8" t="n">
-        <v>8.6364</v>
+        <v>9.7273</v>
       </c>
       <c r="H8" t="n">
-        <v>348.3636</v>
+        <v>384.0909</v>
       </c>
       <c r="I8" t="n">
-        <v>900.9091</v>
+        <v>947.0909</v>
       </c>
       <c r="J8" t="n">
-        <v>0.03751105</v>
+        <v>0.03915667</v>
       </c>
       <c r="K8" t="n">
         <v>221.5717</v>
@@ -1319,63 +1411,75 @@
         <v>0.9972</v>
       </c>
       <c r="P8" t="n">
-        <v>0.03965443</v>
+        <v>0.04338631</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.0404533</v>
+        <v>0.04234058</v>
       </c>
       <c r="R8" t="n">
-        <v>4.0142</v>
+        <v>4.426</v>
       </c>
       <c r="S8" t="n">
-        <v>302.2727</v>
+        <v>345.7273</v>
       </c>
       <c r="T8" t="n">
-        <v>674.4545000000001</v>
+        <v>753</v>
       </c>
       <c r="U8" t="n">
-        <v>393.8255</v>
+        <v>433.334</v>
       </c>
       <c r="V8" t="n">
-        <v>1017.4285</v>
+        <v>1069.4368</v>
       </c>
       <c r="W8" t="n">
-        <v>8.3636</v>
+        <v>9.7273</v>
       </c>
       <c r="X8" t="n">
-        <v>11.0909</v>
+        <v>11.9091</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.8182</v>
+        <v>13.3636</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.0424887</v>
+        <v>0.04426246</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.03854185</v>
-      </c>
-      <c r="AC8" t="inlineStr">
+        <v>0.03877941</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>12.3636</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>205</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="AG8" t="inlineStr">
         <is>
           <t>682_z23</t>
         </is>
       </c>
-      <c r="AD8" t="n">
-        <v>7.7464</v>
-      </c>
-      <c r="AE8" t="n">
+      <c r="AH8" t="n">
+        <v>7.8311</v>
+      </c>
+      <c r="AI8" t="n">
         <v>8</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AJ8" t="n">
         <v>4.4721</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AK8" t="n">
         <v>10.198</v>
       </c>
-      <c r="AH8" t="n">
-        <v>36990</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>7.1663</v>
+      <c r="AL8" t="n">
+        <v>37218</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>7.1953</v>
       </c>
     </row>
     <row r="9">
@@ -1404,16 +1508,16 @@
         <v>1511.5</v>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>7.8462</v>
       </c>
       <c r="H9" t="n">
-        <v>299.6154</v>
+        <v>312.9231</v>
       </c>
       <c r="I9" t="n">
-        <v>749.4615</v>
+        <v>777.4615</v>
       </c>
       <c r="J9" t="n">
-        <v>0.03603597</v>
+        <v>0.03682602</v>
       </c>
       <c r="K9" t="n">
         <v>186.0541</v>
@@ -1431,63 +1535,75 @@
         <v>0.9839</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03944967</v>
+        <v>0.04131445</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03909379</v>
+        <v>0.04045698</v>
       </c>
       <c r="R9" t="n">
-        <v>3.8347</v>
+        <v>4.2332</v>
       </c>
       <c r="S9" t="n">
-        <v>257.3846</v>
+        <v>279.9231</v>
       </c>
       <c r="T9" t="n">
-        <v>560.7692</v>
+        <v>639.6154</v>
       </c>
       <c r="U9" t="n">
-        <v>335.9725</v>
+        <v>350.5151</v>
       </c>
       <c r="V9" t="n">
-        <v>842.489</v>
+        <v>874.2346</v>
       </c>
       <c r="W9" t="n">
-        <v>7.1538</v>
+        <v>7.5385</v>
       </c>
       <c r="X9" t="n">
-        <v>9.8462</v>
+        <v>9.692299999999999</v>
       </c>
       <c r="Y9" t="n">
-        <v>11</v>
+        <v>11.2308</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.04073355</v>
+        <v>0.04158214</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.03647435</v>
-      </c>
-      <c r="AC9" t="inlineStr">
+        <v>0.03711846</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>10.2308</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.2228</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>165</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>682_z29</t>
         </is>
       </c>
-      <c r="AD9" t="n">
-        <v>7.6752</v>
-      </c>
-      <c r="AE9" t="n">
+      <c r="AH9" t="n">
+        <v>7.6905</v>
+      </c>
+      <c r="AI9" t="n">
         <v>8</v>
       </c>
-      <c r="AF9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG9" t="n">
+      <c r="AJ9" t="n">
+        <v>4.4721</v>
+      </c>
+      <c r="AK9" t="n">
         <v>10.198</v>
       </c>
-      <c r="AH9" t="n">
-        <v>34543</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>7.0396</v>
+      <c r="AL9" t="n">
+        <v>35153</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>7.1965</v>
       </c>
     </row>
   </sheetData>
